--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125605789</v>
+        <v>125617186</v>
       </c>
       <c r="B2" t="n">
-        <v>91184</v>
+        <v>80028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>801423</v>
+        <v>801555</v>
       </c>
       <c r="R2" t="n">
-        <v>7284275</v>
+        <v>7284124</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,11 +764,6 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera stora, mycket gamla fruktkroppar på en granstam</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,25 +774,15 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Corina Delling</t>
+          <t>Anne Rebotzke</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Corina Delling</t>
+          <t>Anne Rebotzke</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -918,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125607110</v>
+        <v>125607838</v>
       </c>
       <c r="B4" t="n">
-        <v>57632</v>
+        <v>58111</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,33 +919,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -974,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>801255</v>
+        <v>801173</v>
       </c>
       <c r="R4" t="n">
-        <v>7284437</v>
+        <v>7284308</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1036,7 +1025,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125616159</v>
+        <v>125607110</v>
       </c>
       <c r="B5" t="n">
         <v>57632</v>
@@ -1069,25 +1058,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>801431</v>
+        <v>801255</v>
       </c>
       <c r="R5" t="n">
-        <v>7284123</v>
+        <v>7284437</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1146,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125616304</v>
+        <v>125603041</v>
       </c>
       <c r="B6" t="n">
-        <v>57793</v>
+        <v>80028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,54 +1159,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801469</v>
+        <v>801478</v>
       </c>
       <c r="R6" t="n">
-        <v>7284138</v>
+        <v>7284209</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1244,34 +1232,50 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stor lavväxt längs en aspstam, troligen mycket gammal (Foto!)</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anne Rebotzke</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anne Rebotzke</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125617875</v>
+        <v>125616783</v>
       </c>
       <c r="B7" t="n">
-        <v>58305</v>
+        <v>57632</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,20 +1284,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1303,14 +1307,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1324,13 +1328,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801438</v>
+        <v>801555</v>
       </c>
       <c r="R7" t="n">
-        <v>7284300</v>
+        <v>7284043</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125607186</v>
+        <v>125608358</v>
       </c>
       <c r="B8" t="n">
-        <v>91184</v>
+        <v>58111</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,35 +1406,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>103018</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
@@ -1440,7 +1453,7 @@
         <v>801255</v>
       </c>
       <c r="R8" t="n">
-        <v>7284437</v>
+        <v>7284167</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1481,7 +1494,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1500,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125617906</v>
+        <v>125605789</v>
       </c>
       <c r="B9" t="n">
-        <v>58111</v>
+        <v>91184</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1516,53 +1528,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103018</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801438</v>
+        <v>801423</v>
       </c>
       <c r="R9" t="n">
-        <v>7284300</v>
+        <v>7284275</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1594,31 +1601,47 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Flera stora, mycket gamla fruktkroppar på en granstam</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anne Rebotzke</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anne Rebotzke</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125616783</v>
+        <v>125616159</v>
       </c>
       <c r="B10" t="n">
         <v>57632</v>
@@ -1651,33 +1674,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>801555</v>
+        <v>801431</v>
       </c>
       <c r="R10" t="n">
-        <v>7284043</v>
+        <v>7284123</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1736,10 +1751,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125607838</v>
+        <v>125617875</v>
       </c>
       <c r="B11" t="n">
-        <v>58111</v>
+        <v>58305</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,25 +1763,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1775,14 +1790,10 @@
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1796,13 +1807,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801173</v>
+        <v>801438</v>
       </c>
       <c r="R11" t="n">
-        <v>7284308</v>
+        <v>7284300</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1858,7 +1869,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125608358</v>
+        <v>125617906</v>
       </c>
       <c r="B12" t="n">
         <v>58111</v>
@@ -1897,14 +1908,10 @@
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1918,13 +1925,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801255</v>
+        <v>801438</v>
       </c>
       <c r="R12" t="n">
-        <v>7284167</v>
+        <v>7284300</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1980,10 +1987,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125617186</v>
+        <v>125616304</v>
       </c>
       <c r="B13" t="n">
-        <v>80028</v>
+        <v>57793</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1996,45 +2003,54 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801555</v>
+        <v>801469</v>
       </c>
       <c r="R13" t="n">
-        <v>7284124</v>
+        <v>7284138</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2075,7 +2091,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2094,10 +2109,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125617065</v>
+        <v>125607186</v>
       </c>
       <c r="B14" t="n">
-        <v>56828</v>
+        <v>91184</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2110,50 +2125,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801589</v>
+        <v>801255</v>
       </c>
       <c r="R14" t="n">
-        <v>7284033</v>
+        <v>7284437</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2194,6 +2204,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2212,10 +2223,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125608315</v>
+        <v>125617065</v>
       </c>
       <c r="B15" t="n">
-        <v>57632</v>
+        <v>56828</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2228,16 +2239,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2245,25 +2256,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>801254</v>
+        <v>801589</v>
       </c>
       <c r="R15" t="n">
-        <v>7284212</v>
+        <v>7284033</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2322,10 +2341,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125603041</v>
+        <v>125608315</v>
       </c>
       <c r="B16" t="n">
-        <v>80028</v>
+        <v>57632</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2338,34 +2357,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2373,10 +2389,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801478</v>
+        <v>801254</v>
       </c>
       <c r="R16" t="n">
-        <v>7284209</v>
+        <v>7284212</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2411,40 +2427,24 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Stor lavväxt längs en aspstam, troligen mycket gammal (Foto!)</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Corina Delling</t>
+          <t>Anne Rebotzke</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Corina Delling</t>
+          <t>Anne Rebotzke</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125617186</v>
+        <v>125617906</v>
       </c>
       <c r="B2" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,48 +686,53 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>103018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>801555</v>
+        <v>801438</v>
       </c>
       <c r="R2" t="n">
-        <v>7284124</v>
+        <v>7284300</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,7 +770,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,15 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125608401</v>
+        <v>125616304</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,29 +799,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -841,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801042</v>
+        <v>801469</v>
       </c>
       <c r="R3" t="n">
-        <v>7284083</v>
+        <v>7284138</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -903,15 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125607838</v>
+        <v>125608315</v>
       </c>
       <c r="B4" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,54 +916,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>801173</v>
+        <v>801254</v>
       </c>
       <c r="R4" t="n">
-        <v>7284308</v>
+        <v>7284212</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1028,12 +1013,7 @@
         <v>125607110</v>
       </c>
       <c r="B5" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,15 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125603041</v>
+        <v>125616159</v>
       </c>
       <c r="B6" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,34 +1134,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1194,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801478</v>
+        <v>801431</v>
       </c>
       <c r="R6" t="n">
-        <v>7284209</v>
+        <v>7284123</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1232,55 +1204,34 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stor lavväxt längs en aspstam, troligen mycket gammal (Foto!)</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Corina Delling</t>
+          <t>Anne Rebotzke</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Corina Delling</t>
+          <t>Anne Rebotzke</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125616783</v>
+        <v>125607838</v>
       </c>
       <c r="B7" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,33 +1239,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1328,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801555</v>
+        <v>801173</v>
       </c>
       <c r="R7" t="n">
-        <v>7284043</v>
+        <v>7284308</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1390,15 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125608358</v>
+        <v>125616783</v>
       </c>
       <c r="B8" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,37 +1356,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1450,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>801255</v>
+        <v>801555</v>
       </c>
       <c r="R8" t="n">
-        <v>7284167</v>
+        <v>7284043</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1512,15 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125605789</v>
+        <v>125617186</v>
       </c>
       <c r="B9" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,31 +1469,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1563,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801423</v>
+        <v>801555</v>
       </c>
       <c r="R9" t="n">
-        <v>7284275</v>
+        <v>7284124</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1601,11 +1542,6 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Flera stora, mycket gamla fruktkroppar på en granstam</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1616,40 +1552,25 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Corina Delling</t>
+          <t>Anne Rebotzke</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Corina Delling</t>
+          <t>Anne Rebotzke</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125616159</v>
+        <v>125608358</v>
       </c>
       <c r="B10" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,42 +1578,54 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>801431</v>
+        <v>801255</v>
       </c>
       <c r="R10" t="n">
-        <v>7284123</v>
+        <v>7284167</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1751,32 +1684,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125617875</v>
+        <v>125617065</v>
       </c>
       <c r="B11" t="n">
-        <v>58305</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56834</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103044</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1786,14 +1714,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1807,13 +1735,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801438</v>
+        <v>801589</v>
       </c>
       <c r="R11" t="n">
-        <v>7284300</v>
+        <v>7284033</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1869,37 +1797,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125617906</v>
+        <v>125617875</v>
       </c>
       <c r="B12" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1987,15 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125616304</v>
+        <v>125603041</v>
       </c>
       <c r="B13" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2003,54 +1921,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801469</v>
+        <v>801478</v>
       </c>
       <c r="R13" t="n">
-        <v>7284138</v>
+        <v>7284209</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2085,24 +1994,40 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Stor lavväxt längs en aspstam, troligen mycket gammal (Foto!)</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anne Rebotzke</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anne Rebotzke</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2112,12 +2037,7 @@
         <v>125607186</v>
       </c>
       <c r="B14" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2223,15 +2143,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125617065</v>
+        <v>125605789</v>
       </c>
       <c r="B15" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,50 +2154,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>801589</v>
+        <v>801423</v>
       </c>
       <c r="R15" t="n">
-        <v>7284033</v>
+        <v>7284275</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2317,39 +2227,50 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Flera stora, mycket gamla fruktkroppar på en granstam</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anne Rebotzke</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anne Rebotzke</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125608315</v>
+        <v>125608401</v>
       </c>
       <c r="B16" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,17 +2303,21 @@
           <t>permanent revir</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801254</v>
+        <v>801042</v>
       </c>
       <c r="R16" t="n">
-        <v>7284212</v>
+        <v>7284083</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -1684,27 +1684,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125617065</v>
+        <v>125617875</v>
       </c>
       <c r="B11" t="n">
-        <v>56834</v>
+        <v>58325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801589</v>
+        <v>801438</v>
       </c>
       <c r="R11" t="n">
-        <v>7284033</v>
+        <v>7284300</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,27 +1797,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125617875</v>
+        <v>125617065</v>
       </c>
       <c r="B12" t="n">
-        <v>58325</v>
+        <v>56834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1827,14 +1827,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801438</v>
+        <v>801589</v>
       </c>
       <c r="R12" t="n">
-        <v>7284300</v>
+        <v>7284033</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125617906</v>
+        <v>125616304</v>
       </c>
       <c r="B2" t="n">
-        <v>58129</v>
+        <v>57811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -709,7 +709,11 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>par i lämplig häckbiotop</t>
@@ -726,13 +730,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>801438</v>
+        <v>801469</v>
       </c>
       <c r="R2" t="n">
-        <v>7284300</v>
+        <v>7284138</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -788,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125616304</v>
+        <v>125617906</v>
       </c>
       <c r="B3" t="n">
-        <v>57811</v>
+        <v>58129</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -822,11 +826,7 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>par i lämplig häckbiotop</t>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801469</v>
+        <v>801438</v>
       </c>
       <c r="R3" t="n">
-        <v>7284138</v>
+        <v>7284300</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125607110</v>
+        <v>125616159</v>
       </c>
       <c r="B5" t="n">
         <v>57648</v>
@@ -1038,33 +1038,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>801255</v>
+        <v>801431</v>
       </c>
       <c r="R5" t="n">
-        <v>7284437</v>
+        <v>7284123</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125616159</v>
+        <v>125607110</v>
       </c>
       <c r="B6" t="n">
         <v>57648</v>
@@ -1151,25 +1143,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801431</v>
+        <v>801255</v>
       </c>
       <c r="R6" t="n">
-        <v>7284123</v>
+        <v>7284437</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125617186</v>
+        <v>125608358</v>
       </c>
       <c r="B9" t="n">
-        <v>80070</v>
+        <v>58129</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,45 +1469,54 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>103018</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801555</v>
+        <v>801255</v>
       </c>
       <c r="R9" t="n">
-        <v>7284124</v>
+        <v>7284167</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1548,7 +1557,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1567,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125608358</v>
+        <v>125617186</v>
       </c>
       <c r="B10" t="n">
-        <v>58129</v>
+        <v>80070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,54 +1586,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103018</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>801255</v>
+        <v>801555</v>
       </c>
       <c r="R10" t="n">
-        <v>7284167</v>
+        <v>7284124</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1666,6 +1665,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125603041</v>
+        <v>125607186</v>
       </c>
       <c r="B13" t="n">
-        <v>80070</v>
+        <v>91245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,31 +1921,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801478</v>
+        <v>801255</v>
       </c>
       <c r="R13" t="n">
-        <v>7284209</v>
+        <v>7284437</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1994,11 +1994,6 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Stor lavväxt längs en aspstam, troligen mycket gammal (Foto!)</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2009,35 +2004,25 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Corina Delling</t>
+          <t>Anne Rebotzke</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Corina Delling</t>
+          <t>Anne Rebotzke</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125607186</v>
+        <v>125603041</v>
       </c>
       <c r="B14" t="n">
-        <v>91238</v>
+        <v>80070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,31 +2030,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2080,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801255</v>
+        <v>801478</v>
       </c>
       <c r="R14" t="n">
-        <v>7284437</v>
+        <v>7284209</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2118,6 +2103,11 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Stor lavväxt längs en aspstam, troligen mycket gammal (Foto!)</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2128,15 +2118,25 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
+        </is>
+      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anne Rebotzke</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anne Rebotzke</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2146,7 +2146,7 @@
         <v>125605789</v>
       </c>
       <c r="B15" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -1910,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125607186</v>
+        <v>125603041</v>
       </c>
       <c r="B13" t="n">
-        <v>91245</v>
+        <v>80070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,31 +1921,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801255</v>
+        <v>801478</v>
       </c>
       <c r="R13" t="n">
-        <v>7284437</v>
+        <v>7284209</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1994,6 +1994,11 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Stor lavväxt längs en aspstam, troligen mycket gammal (Foto!)</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2004,25 +2009,35 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anne Rebotzke</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anne Rebotzke</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125603041</v>
+        <v>125607186</v>
       </c>
       <c r="B14" t="n">
-        <v>80070</v>
+        <v>91245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,31 +2045,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2065,10 +2080,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801478</v>
+        <v>801255</v>
       </c>
       <c r="R14" t="n">
-        <v>7284209</v>
+        <v>7284437</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2103,11 +2118,6 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Stor lavväxt längs en aspstam, troligen mycket gammal (Foto!)</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2118,25 +2128,15 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Corina Delling</t>
+          <t>Anne Rebotzke</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Corina Delling</t>
+          <t>Anne Rebotzke</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>125617906</v>
       </c>
       <c r="B3" t="n">
-        <v>58129</v>
+        <v>58130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>125607838</v>
       </c>
       <c r="B7" t="n">
-        <v>58129</v>
+        <v>58130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125608358</v>
+        <v>125617186</v>
       </c>
       <c r="B9" t="n">
-        <v>58129</v>
+        <v>80071</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,54 +1469,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103018</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801255</v>
+        <v>801555</v>
       </c>
       <c r="R9" t="n">
-        <v>7284167</v>
+        <v>7284124</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1557,6 +1548,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125617186</v>
+        <v>125608358</v>
       </c>
       <c r="B10" t="n">
-        <v>80070</v>
+        <v>58130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,45 +1578,54 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>103018</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>801555</v>
+        <v>801255</v>
       </c>
       <c r="R10" t="n">
-        <v>7284124</v>
+        <v>7284167</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1665,7 +1666,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1684,27 +1684,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125617875</v>
+        <v>125617065</v>
       </c>
       <c r="B11" t="n">
-        <v>58325</v>
+        <v>56834</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103044</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801438</v>
+        <v>801589</v>
       </c>
       <c r="R11" t="n">
-        <v>7284300</v>
+        <v>7284033</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,27 +1797,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125617065</v>
+        <v>125617875</v>
       </c>
       <c r="B12" t="n">
-        <v>56834</v>
+        <v>58326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1827,14 +1827,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801589</v>
+        <v>801438</v>
       </c>
       <c r="R12" t="n">
-        <v>7284033</v>
+        <v>7284300</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125603041</v>
+        <v>125607186</v>
       </c>
       <c r="B13" t="n">
-        <v>80070</v>
+        <v>91246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,31 +1921,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801478</v>
+        <v>801255</v>
       </c>
       <c r="R13" t="n">
-        <v>7284209</v>
+        <v>7284437</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1994,11 +1994,6 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Stor lavväxt längs en aspstam, troligen mycket gammal (Foto!)</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2009,35 +2004,25 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Corina Delling</t>
+          <t>Anne Rebotzke</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Corina Delling</t>
+          <t>Anne Rebotzke</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125607186</v>
+        <v>125603041</v>
       </c>
       <c r="B14" t="n">
-        <v>91245</v>
+        <v>80071</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,31 +2030,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2080,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801255</v>
+        <v>801478</v>
       </c>
       <c r="R14" t="n">
-        <v>7284437</v>
+        <v>7284209</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2118,6 +2103,11 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Stor lavväxt längs en aspstam, troligen mycket gammal (Foto!)</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2128,15 +2118,25 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
+        </is>
+      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anne Rebotzke</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anne Rebotzke</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2146,7 +2146,7 @@
         <v>125605789</v>
       </c>
       <c r="B15" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -1458,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125617186</v>
+        <v>125608358</v>
       </c>
       <c r="B9" t="n">
-        <v>80071</v>
+        <v>58130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,45 +1469,54 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>103018</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801555</v>
+        <v>801255</v>
       </c>
       <c r="R9" t="n">
-        <v>7284124</v>
+        <v>7284167</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1548,7 +1557,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1567,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125608358</v>
+        <v>125617186</v>
       </c>
       <c r="B10" t="n">
-        <v>58130</v>
+        <v>80071</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,54 +1586,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103018</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>801255</v>
+        <v>801555</v>
       </c>
       <c r="R10" t="n">
-        <v>7284167</v>
+        <v>7284124</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1666,6 +1665,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -1578,7 +1578,7 @@
         <v>125617186</v>
       </c>
       <c r="B10" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,27 +1684,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125617065</v>
+        <v>125617875</v>
       </c>
       <c r="B11" t="n">
-        <v>56834</v>
+        <v>58326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801589</v>
+        <v>801438</v>
       </c>
       <c r="R11" t="n">
-        <v>7284033</v>
+        <v>7284300</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,27 +1797,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125617875</v>
+        <v>125617065</v>
       </c>
       <c r="B12" t="n">
-        <v>58326</v>
+        <v>56834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1827,14 +1827,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801438</v>
+        <v>801589</v>
       </c>
       <c r="R12" t="n">
-        <v>7284300</v>
+        <v>7284033</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125607186</v>
+        <v>125603041</v>
       </c>
       <c r="B13" t="n">
-        <v>91246</v>
+        <v>80075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,31 +1921,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801255</v>
+        <v>801478</v>
       </c>
       <c r="R13" t="n">
-        <v>7284437</v>
+        <v>7284209</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1994,6 +1994,11 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Stor lavväxt längs en aspstam, troligen mycket gammal (Foto!)</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2004,25 +2009,35 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anne Rebotzke</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anne Rebotzke</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125603041</v>
+        <v>125607186</v>
       </c>
       <c r="B14" t="n">
-        <v>80071</v>
+        <v>91250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,31 +2045,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2065,10 +2080,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801478</v>
+        <v>801255</v>
       </c>
       <c r="R14" t="n">
-        <v>7284209</v>
+        <v>7284437</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2103,11 +2118,6 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Stor lavväxt längs en aspstam, troligen mycket gammal (Foto!)</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2118,25 +2128,15 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Corina Delling</t>
+          <t>Anne Rebotzke</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Corina Delling</t>
+          <t>Anne Rebotzke</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2146,7 +2146,7 @@
         <v>125605789</v>
       </c>
       <c r="B15" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -1684,27 +1684,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125617875</v>
+        <v>125617065</v>
       </c>
       <c r="B11" t="n">
-        <v>58326</v>
+        <v>56834</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103044</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801438</v>
+        <v>801589</v>
       </c>
       <c r="R11" t="n">
-        <v>7284300</v>
+        <v>7284033</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,27 +1797,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125617065</v>
+        <v>125617875</v>
       </c>
       <c r="B12" t="n">
-        <v>56834</v>
+        <v>58326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1827,14 +1827,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801589</v>
+        <v>801438</v>
       </c>
       <c r="R12" t="n">
-        <v>7284033</v>
+        <v>7284300</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -1458,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125608358</v>
+        <v>125617186</v>
       </c>
       <c r="B9" t="n">
-        <v>58130</v>
+        <v>80075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,54 +1469,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103018</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801255</v>
+        <v>801555</v>
       </c>
       <c r="R9" t="n">
-        <v>7284167</v>
+        <v>7284124</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1557,6 +1548,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125617186</v>
+        <v>125608358</v>
       </c>
       <c r="B10" t="n">
-        <v>80075</v>
+        <v>58130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,45 +1578,54 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>103018</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>801555</v>
+        <v>801255</v>
       </c>
       <c r="R10" t="n">
-        <v>7284124</v>
+        <v>7284167</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1665,7 +1666,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1684,27 +1684,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125617065</v>
+        <v>125617875</v>
       </c>
       <c r="B11" t="n">
-        <v>56834</v>
+        <v>58326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801589</v>
+        <v>801438</v>
       </c>
       <c r="R11" t="n">
-        <v>7284033</v>
+        <v>7284300</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,27 +1797,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125617875</v>
+        <v>125617065</v>
       </c>
       <c r="B12" t="n">
-        <v>58326</v>
+        <v>56834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1827,14 +1827,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801438</v>
+        <v>801589</v>
       </c>
       <c r="R12" t="n">
-        <v>7284300</v>
+        <v>7284033</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125616304</v>
+        <v>125617906</v>
       </c>
       <c r="B2" t="n">
-        <v>57811</v>
+        <v>58131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -709,11 +709,7 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>par i lämplig häckbiotop</t>
@@ -730,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>801469</v>
+        <v>801438</v>
       </c>
       <c r="R2" t="n">
-        <v>7284138</v>
+        <v>7284300</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -792,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125617906</v>
+        <v>125616304</v>
       </c>
       <c r="B3" t="n">
-        <v>58130</v>
+        <v>57812</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +799,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -826,7 +822,11 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>par i lämplig häckbiotop</t>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801438</v>
+        <v>801469</v>
       </c>
       <c r="R3" t="n">
-        <v>7284300</v>
+        <v>7284138</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>125608315</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>125616159</v>
       </c>
       <c r="B5" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>125607110</v>
       </c>
       <c r="B6" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>125607838</v>
       </c>
       <c r="B7" t="n">
-        <v>58130</v>
+        <v>58131</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>125616783</v>
       </c>
       <c r="B8" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>125617186</v>
       </c>
       <c r="B9" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>125608358</v>
       </c>
       <c r="B10" t="n">
-        <v>58130</v>
+        <v>58131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,27 +1684,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125617875</v>
+        <v>125617065</v>
       </c>
       <c r="B11" t="n">
-        <v>58326</v>
+        <v>56835</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103044</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801438</v>
+        <v>801589</v>
       </c>
       <c r="R11" t="n">
-        <v>7284300</v>
+        <v>7284033</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,27 +1797,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125617065</v>
+        <v>125617875</v>
       </c>
       <c r="B12" t="n">
-        <v>56834</v>
+        <v>58327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1827,14 +1827,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801589</v>
+        <v>801438</v>
       </c>
       <c r="R12" t="n">
-        <v>7284033</v>
+        <v>7284300</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>125603041</v>
       </c>
       <c r="B13" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>125607186</v>
       </c>
       <c r="B14" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>125605789</v>
       </c>
       <c r="B15" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>125608401</v>
       </c>
       <c r="B16" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -1684,27 +1684,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125617065</v>
+        <v>125617875</v>
       </c>
       <c r="B11" t="n">
-        <v>56835</v>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801589</v>
+        <v>801438</v>
       </c>
       <c r="R11" t="n">
-        <v>7284033</v>
+        <v>7284300</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,27 +1797,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125617875</v>
+        <v>125617065</v>
       </c>
       <c r="B12" t="n">
-        <v>58327</v>
+        <v>56835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1827,14 +1827,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801438</v>
+        <v>801589</v>
       </c>
       <c r="R12" t="n">
-        <v>7284300</v>
+        <v>7284033</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125617906</v>
+        <v>125616304</v>
       </c>
       <c r="B2" t="n">
-        <v>58131</v>
+        <v>57812</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -709,7 +709,11 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>par i lämplig häckbiotop</t>
@@ -726,13 +730,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>801438</v>
+        <v>801469</v>
       </c>
       <c r="R2" t="n">
-        <v>7284300</v>
+        <v>7284138</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -788,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125616304</v>
+        <v>125617906</v>
       </c>
       <c r="B3" t="n">
-        <v>57812</v>
+        <v>58131</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -822,11 +826,7 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>par i lämplig häckbiotop</t>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801469</v>
+        <v>801438</v>
       </c>
       <c r="R3" t="n">
-        <v>7284138</v>
+        <v>7284300</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125616159</v>
+        <v>125607110</v>
       </c>
       <c r="B5" t="n">
         <v>57649</v>
@@ -1038,25 +1038,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>801431</v>
+        <v>801255</v>
       </c>
       <c r="R5" t="n">
-        <v>7284123</v>
+        <v>7284437</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125607110</v>
+        <v>125616159</v>
       </c>
       <c r="B6" t="n">
         <v>57649</v>
@@ -1143,33 +1151,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801255</v>
+        <v>801431</v>
       </c>
       <c r="R6" t="n">
-        <v>7284437</v>
+        <v>7284123</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1684,27 +1684,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125617875</v>
+        <v>125617065</v>
       </c>
       <c r="B11" t="n">
-        <v>58327</v>
+        <v>56835</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103044</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801438</v>
+        <v>801589</v>
       </c>
       <c r="R11" t="n">
-        <v>7284300</v>
+        <v>7284033</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,27 +1797,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125617065</v>
+        <v>125617875</v>
       </c>
       <c r="B12" t="n">
-        <v>56835</v>
+        <v>58327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1827,14 +1827,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801589</v>
+        <v>801438</v>
       </c>
       <c r="R12" t="n">
-        <v>7284033</v>
+        <v>7284300</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>125607186</v>
       </c>
       <c r="B14" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>125605789</v>
       </c>
       <c r="B15" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -1458,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125617186</v>
+        <v>125608358</v>
       </c>
       <c r="B9" t="n">
-        <v>80076</v>
+        <v>58131</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,45 +1469,54 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>103018</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801555</v>
+        <v>801255</v>
       </c>
       <c r="R9" t="n">
-        <v>7284124</v>
+        <v>7284167</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1548,7 +1557,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1567,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125608358</v>
+        <v>125617186</v>
       </c>
       <c r="B10" t="n">
-        <v>58131</v>
+        <v>80076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,54 +1586,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103018</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>801255</v>
+        <v>801555</v>
       </c>
       <c r="R10" t="n">
-        <v>7284167</v>
+        <v>7284124</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1666,6 +1665,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1684,27 +1684,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125617065</v>
+        <v>125617875</v>
       </c>
       <c r="B11" t="n">
-        <v>56835</v>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801589</v>
+        <v>801438</v>
       </c>
       <c r="R11" t="n">
-        <v>7284033</v>
+        <v>7284300</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,27 +1797,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125617875</v>
+        <v>125617065</v>
       </c>
       <c r="B12" t="n">
-        <v>58327</v>
+        <v>56835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1827,14 +1827,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801438</v>
+        <v>801589</v>
       </c>
       <c r="R12" t="n">
-        <v>7284300</v>
+        <v>7284033</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125607110</v>
+        <v>125616159</v>
       </c>
       <c r="B5" t="n">
         <v>57649</v>
@@ -1038,33 +1038,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>801255</v>
+        <v>801431</v>
       </c>
       <c r="R5" t="n">
-        <v>7284437</v>
+        <v>7284123</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125616159</v>
+        <v>125607110</v>
       </c>
       <c r="B6" t="n">
         <v>57649</v>
@@ -1151,25 +1143,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801431</v>
+        <v>801255</v>
       </c>
       <c r="R6" t="n">
-        <v>7284123</v>
+        <v>7284437</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125608358</v>
+        <v>125617186</v>
       </c>
       <c r="B9" t="n">
-        <v>58131</v>
+        <v>80076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,54 +1469,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103018</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801255</v>
+        <v>801555</v>
       </c>
       <c r="R9" t="n">
-        <v>7284167</v>
+        <v>7284124</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1557,6 +1548,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125617186</v>
+        <v>125608358</v>
       </c>
       <c r="B10" t="n">
-        <v>80076</v>
+        <v>58131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,45 +1578,54 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>103018</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>801555</v>
+        <v>801255</v>
       </c>
       <c r="R10" t="n">
-        <v>7284124</v>
+        <v>7284167</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1665,7 +1666,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>125607186</v>
       </c>
       <c r="B14" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>125605789</v>
       </c>
       <c r="B15" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125616159</v>
+        <v>125607838</v>
       </c>
       <c r="B5" t="n">
-        <v>57649</v>
+        <v>58131</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,42 +1021,54 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>801431</v>
+        <v>801173</v>
       </c>
       <c r="R5" t="n">
-        <v>7284123</v>
+        <v>7284308</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125607110</v>
+        <v>125616159</v>
       </c>
       <c r="B6" t="n">
         <v>57649</v>
@@ -1143,33 +1155,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801255</v>
+        <v>801431</v>
       </c>
       <c r="R6" t="n">
-        <v>7284437</v>
+        <v>7284123</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1228,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125607838</v>
+        <v>125607110</v>
       </c>
       <c r="B7" t="n">
-        <v>58131</v>
+        <v>57649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,37 +1243,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801173</v>
+        <v>801255</v>
       </c>
       <c r="R7" t="n">
-        <v>7284308</v>
+        <v>7284437</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>125608315</v>
       </c>
       <c r="B4" t="n">
-        <v>57649</v>
+        <v>57881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>125616159</v>
       </c>
       <c r="B6" t="n">
-        <v>57649</v>
+        <v>57881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>125608401</v>
       </c>
       <c r="B16" t="n">
-        <v>57649</v>
+        <v>57881</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>125608315</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>125616159</v>
       </c>
       <c r="B6" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>125608401</v>
       </c>
       <c r="B16" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>125608315</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>125616159</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>125608401</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>125608315</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>125616159</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>125608401</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>125608315</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>125616159</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>125608401</v>
       </c>
       <c r="B16" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>125608315</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>125616159</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>125608401</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125616304</v>
+        <v>125603041</v>
       </c>
       <c r="B2" t="n">
-        <v>57812</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,54 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>801469</v>
+        <v>801478</v>
       </c>
       <c r="R2" t="n">
-        <v>7284138</v>
+        <v>7284209</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -768,34 +759,50 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Stor lavväxt längs en aspstam, troligen mycket gammal (Foto!)</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anne Rebotzke</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anne Rebotzke</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125617906</v>
+        <v>125617186</v>
       </c>
       <c r="B3" t="n">
-        <v>58131</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,53 +810,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801438</v>
+        <v>801555</v>
       </c>
       <c r="R3" t="n">
-        <v>7284300</v>
+        <v>7284124</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,6 +889,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,14 +908,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125608315</v>
+        <v>125607110</v>
       </c>
       <c r="B4" t="n">
-        <v>57901</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -933,25 +936,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>801254</v>
+        <v>801255</v>
       </c>
       <c r="R4" t="n">
-        <v>7284212</v>
+        <v>7284437</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1010,65 +1021,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125607838</v>
+        <v>125608315</v>
       </c>
       <c r="B5" t="n">
-        <v>58131</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>801173</v>
+        <v>801254</v>
       </c>
       <c r="R5" t="n">
-        <v>7284308</v>
+        <v>7284212</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1127,14 +1126,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125616159</v>
+        <v>125608401</v>
       </c>
       <c r="B6" t="n">
-        <v>57901</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1163,17 +1162,21 @@
           <t>permanent revir</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801431</v>
+        <v>801042</v>
       </c>
       <c r="R6" t="n">
-        <v>7284123</v>
+        <v>7284083</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1232,14 +1235,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125607110</v>
+        <v>125616159</v>
       </c>
       <c r="B7" t="n">
-        <v>57649</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1260,33 +1263,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801255</v>
+        <v>801431</v>
       </c>
       <c r="R7" t="n">
-        <v>7284437</v>
+        <v>7284123</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1348,11 +1343,11 @@
         <v>125616783</v>
       </c>
       <c r="B8" t="n">
-        <v>57649</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1458,56 +1453,61 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125617186</v>
+        <v>125617065</v>
       </c>
       <c r="B9" t="n">
-        <v>80076</v>
+        <v>57132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801555</v>
+        <v>801589</v>
       </c>
       <c r="R9" t="n">
-        <v>7284124</v>
+        <v>7284033</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1548,7 +1548,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1567,14 +1566,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125608358</v>
+        <v>125607838</v>
       </c>
       <c r="B10" t="n">
-        <v>58131</v>
+        <v>58439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1608,7 +1607,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1622,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>801255</v>
+        <v>801173</v>
       </c>
       <c r="R10" t="n">
-        <v>7284167</v>
+        <v>7284308</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1684,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125617875</v>
+        <v>125608358</v>
       </c>
       <c r="B11" t="n">
-        <v>58327</v>
+        <v>58439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1717,14 @@
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1735,13 +1738,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801438</v>
+        <v>801255</v>
       </c>
       <c r="R11" t="n">
-        <v>7284300</v>
+        <v>7284167</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,44 +1800,44 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125617065</v>
+        <v>125617906</v>
       </c>
       <c r="B12" t="n">
-        <v>56835</v>
+        <v>58439</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>103018</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1848,13 +1851,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801589</v>
+        <v>801438</v>
       </c>
       <c r="R12" t="n">
-        <v>7284033</v>
+        <v>7284300</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1910,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125603041</v>
+        <v>125616304</v>
       </c>
       <c r="B13" t="n">
-        <v>80076</v>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,45 +1924,54 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801478</v>
+        <v>801469</v>
       </c>
       <c r="R13" t="n">
-        <v>7284209</v>
+        <v>7284138</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1994,99 +2006,88 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Stor lavväxt längs en aspstam, troligen mycket gammal (Foto!)</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Corina Delling</t>
+          <t>Anne Rebotzke</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Corina Delling</t>
+          <t>Anne Rebotzke</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125607186</v>
+        <v>125617875</v>
       </c>
       <c r="B14" t="n">
-        <v>91256</v>
+        <v>58636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>103044</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801255</v>
+        <v>801438</v>
       </c>
       <c r="R14" t="n">
-        <v>7284437</v>
+        <v>7284300</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2124,7 +2125,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2140,239 +2140,6 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>125605789</v>
-      </c>
-      <c r="B15" t="n">
-        <v>91256</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Kvavisträsket, Nb</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>801423</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7284275</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Piteå</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Norrfjärden</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-05-29</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-05-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Flera stora, mycket gamla fruktkroppar på en granstam</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Artrik, boreal blandskog med urskogs- eller kontinuitetsskogskaraktär, rik på hänglavar, döda stående och liggande träd, på några ställen med övergång till sumpskog</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Corina Delling</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Corina Delling</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>125608401</v>
-      </c>
-      <c r="B16" t="n">
-        <v>57901</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Kvavisträsket, Nb</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>801042</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7284083</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Piteå</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Norrfjärden</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-05-29</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2025-05-29</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Anne Rebotzke</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Anne Rebotzke</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25028-2025 artfynd.xlsx
+++ b/artfynd/A 25028-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125603041</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125617186</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125607110</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125608315</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125608401</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125616159</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,6 +1485,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125616783</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1563,6 +1603,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125617065</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,6 +1725,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125607838</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1797,6 +1847,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125608358</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1910,6 +1965,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125617906</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2027,6 +2087,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125616304</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2140,8 +2205,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125617875</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>